--- a/GearSage-client/rate/excel/baitcasting_reel_detail.xlsx
+++ b/GearSage-client/rate/excel/baitcasting_reel_detail.xlsx
@@ -63474,7 +63474,7 @@
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v/>
+        <v>MRED50002</v>
       </c>
       <c r="B531" t="str">
         <v>MRE5002</v>
@@ -63596,7 +63596,7 @@
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v/>
+        <v>MRED50003</v>
       </c>
       <c r="B532" t="str">
         <v>MRE5003</v>
@@ -63718,7 +63718,7 @@
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v/>
+        <v>MRED50004</v>
       </c>
       <c r="B533" t="str">
         <v>MRE5004</v>
@@ -63840,7 +63840,7 @@
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v/>
+        <v>MRED50005</v>
       </c>
       <c r="B534" t="str">
         <v>MRE5005</v>
@@ -63962,7 +63962,7 @@
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v/>
+        <v>MRED50006</v>
       </c>
       <c r="B535" t="str">
         <v>MRE5006</v>
@@ -64084,7 +64084,7 @@
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v/>
+        <v>MRED50007</v>
       </c>
       <c r="B536" t="str">
         <v>MRE5007</v>
@@ -64206,7 +64206,7 @@
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v/>
+        <v>MRED50008</v>
       </c>
       <c r="B537" t="str">
         <v>MRE5008</v>
@@ -64328,7 +64328,7 @@
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v/>
+        <v>MRED50009</v>
       </c>
       <c r="B538" t="str">
         <v>MRE5009</v>
@@ -64450,7 +64450,7 @@
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v/>
+        <v>MRED50010</v>
       </c>
       <c r="B539" t="str">
         <v>MRE5010</v>
@@ -64572,7 +64572,7 @@
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v/>
+        <v>MRED50011</v>
       </c>
       <c r="B540" t="str">
         <v>MRE5011</v>
@@ -64694,7 +64694,7 @@
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v/>
+        <v>MRED50012</v>
       </c>
       <c r="B541" t="str">
         <v>MRE5012</v>
@@ -64816,7 +64816,7 @@
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v/>
+        <v>MRED50013</v>
       </c>
       <c r="B542" t="str">
         <v>MRE5013</v>
@@ -64938,7 +64938,7 @@
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v/>
+        <v>MRED50014</v>
       </c>
       <c r="B543" t="str">
         <v>MRE5014</v>
@@ -65060,7 +65060,7 @@
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v/>
+        <v>MRED50015</v>
       </c>
       <c r="B544" t="str">
         <v>MRE5015</v>
@@ -65182,7 +65182,7 @@
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v/>
+        <v>MRED50016</v>
       </c>
       <c r="B545" t="str">
         <v>MRE5016</v>
@@ -65304,7 +65304,7 @@
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v/>
+        <v>MRED50017</v>
       </c>
       <c r="B546" t="str">
         <v>MRE5017</v>

--- a/GearSage-client/rate/excel/baitcasting_reel_detail.xlsx
+++ b/GearSage-client/rate/excel/baitcasting_reel_detail.xlsx
@@ -1082,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS546"/>
+  <dimension ref="A1:BF546"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.642857142857141" defaultRowHeight="17.6"/>
   <cols>
     <col width="55.8571428571429" customWidth="1" min="3" max="3"/>
@@ -1326,6 +1326,71 @@
           <t>variant_description</t>
         </is>
       </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>spool_weight_g</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>spool_axis_type</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>knob_size</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>knob_bearing_spec</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>custom_spool_compatibility</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>custom_knob_compatibility</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>handle_knob_material</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>handle_hole_spec</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>main_gear_material</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>main_gear_size</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>minor_gear_material</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>player_environment</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
